--- a/Note/工作摘要.xlsx
+++ b/Note/工作摘要.xlsx
@@ -2164,14 +2164,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2627,28 +2620,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2657,118 +2653,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Note/工作摘要.xlsx
+++ b/Note/工作摘要.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="20250525" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <t>有限个无穷大的和差###不一定###（一定/不一定）是无穷大，有限个无穷小的和差###一定###（一定/不一定）是无穷小</t>
   </si>
   <si>
-    <t>地址线和地址引脚### ###（无需作答）</t>
+    <t>地址线和地址引脚</t>
   </si>
   <si>
     <t>地址线对CPU而言</t>
@@ -159,7 +159,7 @@
     <t>分拆###被积函数###成###多个简化分式###求积分</t>
   </si>
   <si>
-    <t>DRAM相关### ###</t>
+    <t>DRAM相关</t>
   </si>
   <si>
     <t>行/列缓冲区</t>
@@ -180,7 +180,7 @@
     <t>如果用多个芯片，可以提升多数据的###访存速度###</t>
   </si>
   <si>
-    <t>多地址指令个数计算### ###</t>
+    <t>多地址指令个数计算</t>
   </si>
   <si>
     <t>①基础参数明确</t>
@@ -249,7 +249,7 @@
     <t>最长操作码无后续扩展需求，无需预留前缀，其实际最大指令条数 = 自身空间容量 ###cₘ###（所有组合均可使用）</t>
   </si>
   <si>
-    <t>物理信道速率上限### ###</t>
+    <t>物理信道速率上限</t>
   </si>
   <si>
     <t>无噪声：###奈奎斯特采样定理###</t>
@@ -282,7 +282,7 @@
     <t>dB=10*log(10,S/N)，因此要倒过来计算S/N，即###S/N=10^(dB/10)###</t>
   </si>
   <si>
-    <t>对于非空B树而言，只要删除了一个关键字，叶子必然会变动### ###</t>
+    <t>对于非空B树而言，只要删除了一个关键字，叶子必然会变动</t>
   </si>
   <si>
     <t>如果非叶节点删除关键字，无论是否满足关键字个数都会触发###挪用###</t>
@@ -291,7 +291,7 @@
     <t>而挪用对于其它被挪用的非叶节点来说也都会继续触发挪用，直到被挪用节点是###叶节点###</t>
   </si>
   <si>
-    <t>流水线的冒险类型### ###</t>
+    <t>流水线的冒险类型</t>
   </si>
   <si>
     <t>数据冒险：###RAW、WAR、WAW###（针对寄存器）</t>
@@ -330,13 +330,13 @@
     <t>寄存器：###指令译码（从寄存器读取地址偏移量）和写回寄存器阶段###</t>
   </si>
   <si>
-    <t>PC的自增有专门的机构，不依赖ALU### ###</t>
-  </si>
-  <si>
-    <t>CSMA的争用时间片即RTT，可以用这个值计算后续的退避时间### ###</t>
-  </si>
-  <si>
-    <t>ARQ协议### ###</t>
+    <t>PC的自增有专门的机构，不依赖ALU</t>
+  </si>
+  <si>
+    <t>CSMA的争用时间片即RTT，可以用这个值计算后续的退避时间</t>
+  </si>
+  <si>
+    <t>ARQ协议</t>
   </si>
   <si>
     <t>SW（停等）：###单发送窗，单接收窗###，n比特帧序号下，收发窗都是1</t>
@@ -348,13 +348,13 @@
     <t>SR：###多发送窗、多接收窗###（乱序接受），n比特帧序号下，收发窗都是2^(n-1)</t>
   </si>
   <si>
-    <t>QAM-n，后面的数字是同一时刻的波形种类数### ###</t>
-  </si>
-  <si>
-    <t>分组交换的流水线图，平行四边形的倾斜越厉害，传播时延就越大，时延带宽积也越大### ###</t>
-  </si>
-  <si>
-    <t>浮点数的位数分配### ###</t>
+    <t>QAM-n，后面的数字是同一时刻的波形种类数</t>
+  </si>
+  <si>
+    <t>分组交换的流水线图，平行四边形的倾斜越厉害，传播时延就越大，时延带宽积也越大</t>
+  </si>
+  <si>
+    <t>浮点数的位数分配</t>
   </si>
   <si>
     <t>单精度：总计32位，###1位符号位，8位阶码（移码），23位尾数（原码）###</t>
@@ -363,7 +363,7 @@
     <t>双精度：总计64位，###1位符号位，11位阶码（移码），52位尾数（原码）###</t>
   </si>
   <si>
-    <t>UDP校验和方法### ###</t>
+    <t>UDP校验和方法</t>
   </si>
   <si>
     <t>将UDP数据（包括伪首部、UDP首部、UDP数据部分）按###16位为单位拆分成组###</t>
@@ -381,16 +381,16 @@
     <t>对加法的最后和###取反###</t>
   </si>
   <si>
-    <t>MSL（最长报文段寿命）：TCP关闭连接时，客户端一方TIME_WAIT到CLOSED之间时长的一半### ###</t>
-  </si>
-  <si>
-    <t>ARQ协议中，滑动窗口大小与序号的具体数值无关，比如窗口大小4的SR，序号可以是0,1,2,3也可以是1,2,3,4### ###</t>
+    <t>MSL（最长报文段寿命）：TCP关闭连接时，客户端一方TIME_WAIT到CLOSED之间时长的一半</t>
+  </si>
+  <si>
+    <t>ARQ协议中，滑动窗口大小与序号的具体数值无关，比如窗口大小4的SR，序号可以是0,1,2,3也可以是1,2,3,4</t>
   </si>
   <si>
     <t>序号范围由###序号位数###决定</t>
   </si>
   <si>
-    <t>802.11的NAV（网络分配向量）：收到与自己无关的RTS/CTS帧时，设定自己“闭嘴”的时长### ###</t>
+    <t>802.11的NAV（网络分配向量）：收到与自己无关的RTS/CTS帧时，设定自己“闭嘴”的时长</t>
   </si>
   <si>
     <t>NAV时长也就是看“那一对”能谈多久</t>
@@ -585,10 +585,10 @@
     <t>单调性：</t>
   </si>
   <si>
-    <t>∀x1，x2∈D且x1&gt;x2，都有###f(x1)&gt;f(x2)###（单调增加）</t>
-  </si>
-  <si>
-    <t>∀x1，x2∈D且x1&gt;x2，都有###f(x1)&lt;f(x2)###（单调减少）</t>
+    <t>∀x1，x2∈D且x1&gt;x2，都有###f(x1)&gt;=f(x2)###（单调增加）</t>
+  </si>
+  <si>
+    <t>∀x1，x2∈D且x1&gt;x2，都有###f(x1)&lt;=f(x2)###（单调减少）</t>
   </si>
   <si>
     <t>有界性：</t>
@@ -684,7 +684,7 @@
     <t>错题总结20221119</t>
   </si>
   <si>
-    <t>二重积分转极坐标时θ角的积分范围：（无需作答）### ###</t>
+    <t>二重积分转极坐标时θ角的积分范围：</t>
   </si>
   <si>
     <t>①：要检查隐含在区域边界方程的条件</t>
@@ -825,13 +825,13 @@
     <t>错题总结20220303</t>
   </si>
   <si>
-    <t>如果某函数可导或连续，计算时要尽可能将部分表示式化成其函数值或导数定义的结构（无需作答）### ###</t>
+    <t>如果某函数可导或连续，计算时要尽可能将部分表示式化成其函数值或导数定义的结构</t>
   </si>
   <si>
     <t>错题总结20220217</t>
   </si>
   <si>
-    <t>两个无极限函数相加可能会得到有极限函数，反过来不能随意分拆函数（无需作答）### ###</t>
+    <t>两个无极限函数相加可能会得到有极限函数，反过来不能随意分拆函数</t>
   </si>
   <si>
     <t>错题总结20220207</t>
@@ -867,7 +867,7 @@
     <t>每个子网的地址 ### 不能有重叠 ###（填写子网地址的冲突要求）</t>
   </si>
   <si>
-    <t>有效载荷最大传输效率### ###</t>
+    <t>有效载荷最大传输效率</t>
   </si>
   <si>
     <t>考察对象：###端到端###（传输层）</t>
@@ -897,7 +897,7 @@
     <t>TCP头长度会变，最小###20B###，最大###60B###（用来算最小传输效率）</t>
   </si>
   <si>
-    <t>CLOCK算法### ###</t>
+    <t>CLOCK算法</t>
   </si>
   <si>
     <t>基础CLOCK</t>
@@ -966,7 +966,7 @@
     <t>修改位不会主动被置换算法改变</t>
   </si>
   <si>
-    <t>拥塞控制### ###</t>
+    <t>拥塞控制</t>
   </si>
   <si>
     <t>慢启动：从###1###开始，每收到一个有效ACK，cwnd增加###1###，直到到达###ssthresh###（初始###16###）</t>
@@ -993,7 +993,7 @@
     <t>cwnd和ssthresh的单位是###MSS###（最大段长）</t>
   </si>
   <si>
-    <t>字节序号### ###</t>
+    <t>字节序号</t>
   </si>
   <si>
     <t>每次发送的报文###seq字段###=该报文段第一个字节在全部正文中的序号</t>
@@ -1002,7 +1002,7 @@
     <t>确认的###ack_seq字段###=接收方期望下次收到的第一个字节在全部正文的序号</t>
   </si>
   <si>
-    <t>贝尔曼福特（RIP协议）### ###</t>
+    <t>贝尔曼福特（RIP协议的距离向量算法原型）</t>
   </si>
   <si>
     <t>一开始和迪杰斯特拉一样，列表，三个要素</t>
@@ -1026,7 +1026,7 @@
     <t>如果V-1轮迭代后仍有更新，就出现了###负权环###</t>
   </si>
   <si>
-    <t>B树的补丁### ###</t>
+    <t>B树的补丁</t>
   </si>
   <si>
     <t>修复（非叶子节点）触发条件不看关键字个数，###一定会触发###</t>
@@ -1035,7 +1035,7 @@
     <t>修复（叶子节点）触发条件###要看关键字个数###，###未必会触发###</t>
   </si>
   <si>
-    <t>HTTP 1.1和1.0的区别### ###</t>
+    <t>HTTP 1.1和1.0的区别</t>
   </si>
   <si>
     <t>1.0默认###短连接###（每个请求单独TCP连接），1.1默认###KeepAlive###</t>
@@ -1056,10 +1056,10 @@
     <t>正定二次型的顺序主子式###均正###</t>
   </si>
   <si>
-    <t>可导点不可能同时为拐点和极值点### ###（无需作答）</t>
-  </si>
-  <si>
-    <t>互斥手段的原子性### ###</t>
+    <t>可导点不可能同时为拐点和极值点</t>
+  </si>
+  <si>
+    <t>互斥手段的原子性</t>
   </si>
   <si>
     <t>硬件手段都有原子性，但是原子性的来源不同</t>
@@ -1089,7 +1089,7 @@
     <t>系统调用的返回归属于###发起调用的进程###，当返回发生时，该进程处于###执行###态</t>
   </si>
   <si>
-    <t>使用中断的I/O有两种，同步和异步### ###</t>
+    <t>使用中断的I/O有两种，同步和异步</t>
   </si>
   <si>
     <t>同步I/O：进程等待外设发东西，为此阻塞自身不继续执行，比如Python的input()</t>
@@ -1134,7 +1134,7 @@
     <t>TCP握手挥手的每一个报文消耗###一###个字节序号</t>
   </si>
   <si>
-    <t>入度为0的点对于有向图的拓扑排序很重要### ###</t>
+    <t>入度为0的点对于有向图的拓扑排序很重要</t>
   </si>
   <si>
     <t>每次将入度0的点输出并且从原图删除，能够得到拓扑排序</t>
@@ -1152,10 +1152,10 @@
     <t>OF（有符号溢出）的快速判断法：###截掉超出位数的部分，剩下的部分做1位符号扩展，看看和截掉前的是否一样，不一样则说明溢出###</t>
   </si>
   <si>
-    <t>当内存的地址偏移计算后CF=1，则舍掉溢出位，直接用低位范围内的部分作为地址### ###</t>
-  </si>
-  <si>
-    <t>多进程协作类题目需要注意隐含的互斥关系，不要被同步关系吸引了全部的注意力### ###</t>
+    <t>当内存的地址偏移计算后CF=1，则舍掉溢出位，直接用低位范围内的部分作为地址</t>
+  </si>
+  <si>
+    <t>多进程协作类题目需要注意隐含的互斥关系，不要被同步关系吸引了全部的注意力</t>
   </si>
   <si>
     <t>卡特兰数：###C(n,2n)/(n+1)###（C(a,b)=b!/(a!*(b-a)!）</t>
@@ -1185,7 +1185,7 @@
     <t>本质上是操作系统可重定位性导致的</t>
   </si>
   <si>
-    <t>特例法大杀器-一元运算### ###（无需作答）</t>
+    <t>特例法大杀器-一元运算</t>
   </si>
   <si>
     <t>性质排序参考20250616</t>
@@ -1338,13 +1338,13 @@
     <t>考察积分区间是否会被压缩（比如±a上的积分，换元x²）</t>
   </si>
   <si>
-    <t>IO密集型的进程应该优先执行，因为提前让慢的IO先开始可以同时利用CPU并行提效。### ###（无需作答）</t>
-  </si>
-  <si>
-    <t>驻留集大小不是驻留集窗口的大小，驻留集窗口之外的页号，也会被从页框释放掉。### ###（无需作答）</t>
-  </si>
-  <si>
-    <t>fork产生子进程的逻辑### ###（无需作答）</t>
+    <t>IO密集型的进程应该优先执行，因为提前让慢的IO先开始可以同时利用CPU并行提效。</t>
+  </si>
+  <si>
+    <t>驻留集大小不是驻留集窗口的大小，驻留集窗口之外的页号，也会被从页框释放掉。</t>
+  </si>
+  <si>
+    <t>fork产生子进程的逻辑</t>
   </si>
   <si>
     <t>父进程执行fork后，子进程相当于从父进程的fork返回位置开始执行，只是fork返回的pid不同而已。</t>
@@ -1605,7 +1605,7 @@
     <t>CU的输入有两个，除了IR（或者说ID）还有###ALU的输出FR###（填写信号名称）</t>
   </si>
   <si>
-    <t>磁盘的术语### ###</t>
+    <t>磁盘的术语</t>
   </si>
   <si>
     <t>柱面=磁道：所有盘面的同一磁道竖着组成一个柱面，磁道是盘面上的同心圆，不同半径的圆磁道不同</t>
@@ -1695,7 +1695,7 @@
     <t>树高控制的结果</t>
   </si>
   <si>
-    <t>红黑树-旋转### ###（无需作答）</t>
+    <t>红黑树-旋转</t>
   </si>
   <si>
     <t>左旋-逆时针，右旋-顺时针</t>
@@ -1812,7 +1812,7 @@
     <t>黑替黑：？？？</t>
   </si>
   <si>
-    <t>单调有界必有极限是数列才有的性质，函数没有，不能乱用！### ###（无需作答）</t>
+    <t>单调有界必有极限是数列才有的性质，函数没有，不能乱用！</t>
   </si>
   <si>
     <t>遇到函数还有有界性，考虑用###闭区间连续的特性###来推（20240415）</t>
@@ -1830,10 +1830,10 @@
     <t>定积分上下限之差正好为周期的情况下，###任意平移（x±a）###不改变定积分的数值</t>
   </si>
   <si>
-    <t>高阶非齐次不要硬上常数变异，那个只适合一阶（无需作答）### ###</t>
-  </si>
-  <si>
-    <t>高阶齐次求特征根写清楚因式分解，不然重根看不清楚到底是几重！！！（无需作答）### ###</t>
+    <t>高阶非齐次不要硬上常数变异，那个只适合一阶</t>
+  </si>
+  <si>
+    <t>高阶齐次求特征根写清楚因式分解，不然重根看不清楚到底是几重！！！</t>
   </si>
   <si>
     <t>高阶非齐次特解看非齐次项构造</t>
@@ -1881,7 +1881,7 @@
     <t>三坨在一起应该是###(x^k)*((a1*(x^n)+...)*sin(b*x)+(b1*(x^n)+...)*cos(b*x))*exp(a*x)###</t>
   </si>
   <si>
-    <t>特例法大杀器-二元组合### ###（无需作答）</t>
+    <t>特例法大杀器-二元组合</t>
   </si>
   <si>
     <t>一阶或二阶可导（一元）+连续性（一元）</t>
@@ -1950,7 +1950,7 @@
     <t>文件一般来说都有全局唯一的索引节点号，除非是###硬链接###（填写文件链接类型）</t>
   </si>
   <si>
-    <t>一个文件至少占用一个磁盘块，磁盘块不能为多个文件共享### ###</t>
+    <t>一个文件至少占用一个磁盘块，磁盘块不能为多个文件共享</t>
   </si>
   <si>
     <t>磁盘块号记录于索引节点内，索引节点存在于单独的磁盘块（索引节点块）上</t>
@@ -1980,7 +1980,7 @@
     <t>三级间接块存储磁盘块容量：(磁盘块大小/地址长度)*二级间接块存储磁盘块容量</t>
   </si>
   <si>
-    <t>以太网最短帧长和最远距离的关系### ###</t>
+    <t>以太网最短帧长和最远距离的关系</t>
   </si>
   <si>
     <t>要让最短帧在链路上足够久才能被检测，因此最短帧的传输时延要大于RTT</t>
@@ -2019,7 +2019,7 @@
     <t>但如果是地址续租的情况下，不需要通知其它DHCP服务器，就没有广播的理由（因此是单播）</t>
   </si>
   <si>
-    <t>二三层单播/多播组合情形### ###</t>
+    <t>二三层单播/多播组合情形</t>
   </si>
   <si>
     <t>全单播、全多播：略</t>
@@ -2040,7 +2040,7 @@
     <t>有向图的邻接矩阵中，行对应###起点###（填写矩阵行对应元素），列对应###终点###（填写矩阵列对应元素）</t>
   </si>
   <si>
-    <t>置换选择排序=货车垒货，逐车壮哉，每次最大，下大上小### ###</t>
+    <t>置换选择排序=货车垒货，逐车壮哉，每次最大，下大上小</t>
   </si>
   <si>
     <t>如果能放（工作区有比最顶层小的）就一直放（符合条件最大的），放不了就让新一辆车来拉，因此每个归并段长度不一定相等</t>
@@ -2055,7 +2055,7 @@
     <t>###时间局部性###（填写局部性类型）：同一数据被重复访问</t>
   </si>
   <si>
-    <t>根据代码来判断缓存命中次数### ###</t>
+    <t>根据代码来判断缓存命中次数</t>
   </si>
   <si>
     <t>代码里有读取或者赋值的次数就是总的访问次数</t>
@@ -2124,7 +2124,7 @@
     <t>被积函数是周期函数且积分长度为一个周期</t>
   </si>
   <si>
-    <t>那么起点可以任选### ###（无需作答）</t>
+    <t>那么起点可以任选</t>
   </si>
   <si>
     <t>比较定积分大小：</t>

--- a/Note/工作摘要.xlsx
+++ b/Note/工作摘要.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="20250525" sheetId="1" r:id="rId1"/>

--- a/Note/工作摘要.xlsx
+++ b/Note/工作摘要.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="3" activeTab="5"/>
+    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="20250525" sheetId="1" r:id="rId1"/>

--- a/Note/工作摘要.xlsx
+++ b/Note/工作摘要.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="6" activeTab="8"/>
+    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="9" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="20250525" sheetId="1" r:id="rId1"/>

--- a/Note/工作摘要.xlsx
+++ b/Note/工作摘要.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="9" activeTab="9"/>
+    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="11" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="20250525" sheetId="1" r:id="rId1"/>

--- a/Note/工作摘要.xlsx
+++ b/Note/工作摘要.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="11" activeTab="13"/>
+    <workbookView windowWidth="11520" windowHeight="9180" firstSheet="17" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="20250525" sheetId="1" r:id="rId1"/>
